--- a/artfynd/A 59348-2020 artfynd.xlsx
+++ b/artfynd/A 59348-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124719045</v>
+        <v>124718448</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>485262</v>
+        <v>485375</v>
       </c>
       <c r="R2" t="n">
-        <v>6850477</v>
+        <v>6850440</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124718448</v>
+        <v>124717816</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -810,17 +810,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>485375</v>
+        <v>485493</v>
       </c>
       <c r="R3" t="n">
-        <v>6850440</v>
+        <v>6850463</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124718500</v>
+        <v>124717925</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -919,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>485369</v>
+        <v>485493</v>
       </c>
       <c r="R4" t="n">
-        <v>6850446</v>
+        <v>6850455</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124717289</v>
+        <v>124719083</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1014,20 +1023,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485495</v>
+        <v>485248</v>
       </c>
       <c r="R5" t="n">
-        <v>6850520</v>
+        <v>6850480</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,7 +1101,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124718616</v>
+        <v>124718500</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1123,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485358</v>
+        <v>485369</v>
       </c>
       <c r="R6" t="n">
-        <v>6850463</v>
+        <v>6850446</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1203,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124718018</v>
+        <v>124719045</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1218,29 +1236,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>485514</v>
+        <v>485262</v>
       </c>
       <c r="R7" t="n">
-        <v>6850415</v>
+        <v>6850477</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1296,7 +1305,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124716407</v>
+        <v>124718696</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1336,10 +1345,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485304</v>
+        <v>485342</v>
       </c>
       <c r="R8" t="n">
-        <v>6850518</v>
+        <v>6850467</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,7 +1407,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124717925</v>
+        <v>124717545</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1438,13 +1447,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485493</v>
+        <v>485515</v>
       </c>
       <c r="R9" t="n">
-        <v>6850455</v>
+        <v>6850468</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1500,7 +1509,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124717545</v>
+        <v>124718947</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1533,20 +1542,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485515</v>
+        <v>485309</v>
       </c>
       <c r="R10" t="n">
-        <v>6850468</v>
+        <v>6850483</v>
       </c>
       <c r="S10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1602,7 +1620,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124719083</v>
+        <v>124718616</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1635,26 +1653,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>485248</v>
+        <v>485358</v>
       </c>
       <c r="R11" t="n">
-        <v>6850480</v>
+        <v>6850463</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,7 +1722,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124717615</v>
+        <v>124718815</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1746,26 +1755,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485502</v>
+        <v>485309</v>
       </c>
       <c r="R12" t="n">
-        <v>6850463</v>
+        <v>6850480</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1824,7 +1824,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124717758</v>
+        <v>124718385</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1857,20 +1857,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485495</v>
+        <v>485387</v>
       </c>
       <c r="R13" t="n">
-        <v>6850459</v>
+        <v>6850441</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1926,7 +1935,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124718385</v>
+        <v>124717758</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -1959,29 +1968,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485387</v>
+        <v>485495</v>
       </c>
       <c r="R14" t="n">
-        <v>6850441</v>
+        <v>6850459</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124717816</v>
+        <v>124718018</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2086,13 +2086,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485493</v>
+        <v>485514</v>
       </c>
       <c r="R15" t="n">
-        <v>6850463</v>
+        <v>6850415</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124718947</v>
+        <v>124716407</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2181,26 +2181,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>485309</v>
+        <v>485304</v>
       </c>
       <c r="R16" t="n">
-        <v>6850483</v>
+        <v>6850518</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2259,7 +2250,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124718815</v>
+        <v>124717289</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2299,13 +2290,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>485309</v>
+        <v>485495</v>
       </c>
       <c r="R17" t="n">
-        <v>6850480</v>
+        <v>6850520</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2361,7 +2352,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124718696</v>
+        <v>124717615</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2394,17 +2385,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>485342</v>
+        <v>485502</v>
       </c>
       <c r="R18" t="n">
-        <v>6850467</v>
+        <v>6850463</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 59348-2020 artfynd.xlsx
+++ b/artfynd/A 59348-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124718448</v>
+        <v>124717758</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>485375</v>
+        <v>485495</v>
       </c>
       <c r="R2" t="n">
-        <v>6850440</v>
+        <v>6850459</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124717816</v>
+        <v>124718500</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -810,26 +810,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>485493</v>
+        <v>485369</v>
       </c>
       <c r="R3" t="n">
-        <v>6850463</v>
+        <v>6850446</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124717925</v>
+        <v>124716407</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -928,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>485493</v>
+        <v>485304</v>
       </c>
       <c r="R4" t="n">
-        <v>6850455</v>
+        <v>6850518</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124719083</v>
+        <v>124718448</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1023,26 +1014,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485248</v>
+        <v>485375</v>
       </c>
       <c r="R5" t="n">
-        <v>6850480</v>
+        <v>6850440</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124718500</v>
+        <v>124718815</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1141,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485369</v>
+        <v>485309</v>
       </c>
       <c r="R6" t="n">
-        <v>6850446</v>
+        <v>6850480</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124719045</v>
+        <v>124718018</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1236,20 +1218,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>485262</v>
+        <v>485514</v>
       </c>
       <c r="R7" t="n">
-        <v>6850477</v>
+        <v>6850415</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,7 +1296,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124718696</v>
+        <v>124717615</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1338,17 +1329,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485342</v>
+        <v>485502</v>
       </c>
       <c r="R8" t="n">
-        <v>6850467</v>
+        <v>6850463</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,7 +1407,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124717545</v>
+        <v>124718616</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1447,13 +1447,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485515</v>
+        <v>485358</v>
       </c>
       <c r="R9" t="n">
-        <v>6850468</v>
+        <v>6850463</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124718616</v>
+        <v>124719045</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1660,10 +1660,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>485358</v>
+        <v>485262</v>
       </c>
       <c r="R11" t="n">
-        <v>6850463</v>
+        <v>6850477</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124718815</v>
+        <v>124718696</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485309</v>
+        <v>485342</v>
       </c>
       <c r="R12" t="n">
-        <v>6850480</v>
+        <v>6850467</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1824,7 +1824,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124718385</v>
+        <v>124717545</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1857,29 +1857,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485387</v>
+        <v>485515</v>
       </c>
       <c r="R13" t="n">
-        <v>6850441</v>
+        <v>6850468</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1935,7 +1926,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124717758</v>
+        <v>124719083</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -1968,20 +1959,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485495</v>
+        <v>485248</v>
       </c>
       <c r="R14" t="n">
-        <v>6850459</v>
+        <v>6850480</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124718018</v>
+        <v>124718385</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2086,13 +2086,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485514</v>
+        <v>485387</v>
       </c>
       <c r="R15" t="n">
-        <v>6850415</v>
+        <v>6850441</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124716407</v>
+        <v>124717289</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2188,13 +2188,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>485304</v>
+        <v>485495</v>
       </c>
       <c r="R16" t="n">
-        <v>6850518</v>
+        <v>6850520</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124717289</v>
+        <v>124717925</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2290,13 +2290,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>485495</v>
+        <v>485493</v>
       </c>
       <c r="R17" t="n">
-        <v>6850520</v>
+        <v>6850455</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124717615</v>
+        <v>124717816</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2401,7 +2401,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>485502</v>
+        <v>485493</v>
       </c>
       <c r="R18" t="n">
         <v>6850463</v>

--- a/artfynd/A 59348-2020 artfynd.xlsx
+++ b/artfynd/A 59348-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124717758</v>
+        <v>124718947</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -708,20 +708,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>485495</v>
+        <v>485309</v>
       </c>
       <c r="R2" t="n">
-        <v>6850459</v>
+        <v>6850483</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124718500</v>
+        <v>124716407</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -817,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>485369</v>
+        <v>485304</v>
       </c>
       <c r="R3" t="n">
-        <v>6850446</v>
+        <v>6850518</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124716407</v>
+        <v>124718500</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -919,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>485304</v>
+        <v>485369</v>
       </c>
       <c r="R4" t="n">
-        <v>6850518</v>
+        <v>6850446</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124718448</v>
+        <v>124718616</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1021,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485375</v>
+        <v>485358</v>
       </c>
       <c r="R5" t="n">
-        <v>6850440</v>
+        <v>6850463</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1092,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124718815</v>
+        <v>124719045</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1123,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485309</v>
+        <v>485262</v>
       </c>
       <c r="R6" t="n">
-        <v>6850480</v>
+        <v>6850477</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1194,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124718018</v>
+        <v>124718448</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1218,29 +1227,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>485514</v>
+        <v>485375</v>
       </c>
       <c r="R7" t="n">
-        <v>6850415</v>
+        <v>6850440</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124717615</v>
+        <v>124718815</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1329,26 +1329,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485502</v>
+        <v>485309</v>
       </c>
       <c r="R8" t="n">
-        <v>6850463</v>
+        <v>6850480</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,7 +1398,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124718616</v>
+        <v>124717289</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1447,13 +1438,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485358</v>
+        <v>485495</v>
       </c>
       <c r="R9" t="n">
-        <v>6850463</v>
+        <v>6850520</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1509,7 +1500,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124718947</v>
+        <v>124719083</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1544,7 +1535,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1558,10 +1549,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485309</v>
+        <v>485248</v>
       </c>
       <c r="R10" t="n">
-        <v>6850483</v>
+        <v>6850480</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1620,7 +1611,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124719045</v>
+        <v>124717816</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1653,17 +1644,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>485262</v>
+        <v>485493</v>
       </c>
       <c r="R11" t="n">
-        <v>6850477</v>
+        <v>6850463</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124718696</v>
+        <v>124717758</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1762,13 +1762,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485342</v>
+        <v>485495</v>
       </c>
       <c r="R12" t="n">
-        <v>6850467</v>
+        <v>6850459</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124717545</v>
+        <v>124718018</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1857,20 +1857,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485515</v>
+        <v>485514</v>
       </c>
       <c r="R13" t="n">
-        <v>6850468</v>
+        <v>6850415</v>
       </c>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1926,7 +1935,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124719083</v>
+        <v>124717925</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -1959,29 +1968,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485248</v>
+        <v>485493</v>
       </c>
       <c r="R14" t="n">
-        <v>6850480</v>
+        <v>6850455</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124718385</v>
+        <v>124718696</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2070,26 +2070,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485387</v>
+        <v>485342</v>
       </c>
       <c r="R15" t="n">
-        <v>6850441</v>
+        <v>6850467</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,7 +2139,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124717289</v>
+        <v>124717545</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2188,13 +2179,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>485495</v>
+        <v>485515</v>
       </c>
       <c r="R16" t="n">
-        <v>6850520</v>
+        <v>6850468</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2250,7 +2241,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124717925</v>
+        <v>124718385</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2283,20 +2274,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>485493</v>
+        <v>485387</v>
       </c>
       <c r="R17" t="n">
-        <v>6850455</v>
+        <v>6850441</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124717816</v>
+        <v>124717615</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2401,7 +2401,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>485493</v>
+        <v>485502</v>
       </c>
       <c r="R18" t="n">
         <v>6850463</v>

--- a/artfynd/A 59348-2020 artfynd.xlsx
+++ b/artfynd/A 59348-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124718947</v>
+        <v>124717615</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>485309</v>
+        <v>485502</v>
       </c>
       <c r="R2" t="n">
-        <v>6850483</v>
+        <v>6850463</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -888,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124718500</v>
+        <v>124718815</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>485369</v>
+        <v>485309</v>
       </c>
       <c r="R4" t="n">
-        <v>6850446</v>
+        <v>6850480</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124718616</v>
+        <v>124718018</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1023,20 +1023,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485358</v>
+        <v>485514</v>
       </c>
       <c r="R5" t="n">
-        <v>6850463</v>
+        <v>6850415</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,7 +1101,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124719045</v>
+        <v>124718947</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1125,17 +1134,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485262</v>
+        <v>485309</v>
       </c>
       <c r="R6" t="n">
-        <v>6850477</v>
+        <v>6850483</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1212,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124718448</v>
+        <v>124718616</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1234,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>485375</v>
+        <v>485358</v>
       </c>
       <c r="R7" t="n">
-        <v>6850440</v>
+        <v>6850463</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,7 +1314,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124718815</v>
+        <v>124717816</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1329,17 +1347,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485309</v>
+        <v>485493</v>
       </c>
       <c r="R8" t="n">
-        <v>6850480</v>
+        <v>6850463</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,7 +1425,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124717289</v>
+        <v>124718448</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1438,13 +1465,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485495</v>
+        <v>485375</v>
       </c>
       <c r="R9" t="n">
-        <v>6850520</v>
+        <v>6850440</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1611,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124717816</v>
+        <v>124717925</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1644,16 +1671,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
@@ -1663,10 +1681,10 @@
         <v>485493</v>
       </c>
       <c r="R11" t="n">
-        <v>6850463</v>
+        <v>6850455</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1722,7 +1740,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124717758</v>
+        <v>124719045</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1762,13 +1780,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485495</v>
+        <v>485262</v>
       </c>
       <c r="R12" t="n">
-        <v>6850459</v>
+        <v>6850477</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1824,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124718018</v>
+        <v>124717545</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1857,29 +1875,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485514</v>
+        <v>485515</v>
       </c>
       <c r="R13" t="n">
-        <v>6850415</v>
+        <v>6850468</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1935,7 +1944,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124717925</v>
+        <v>124718696</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -1975,13 +1984,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485493</v>
+        <v>485342</v>
       </c>
       <c r="R14" t="n">
-        <v>6850455</v>
+        <v>6850467</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2037,7 +2046,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124718696</v>
+        <v>124718385</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2070,17 +2079,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485342</v>
+        <v>485387</v>
       </c>
       <c r="R15" t="n">
-        <v>6850467</v>
+        <v>6850441</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2139,7 +2157,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124717545</v>
+        <v>124717289</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2179,13 +2197,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>485515</v>
+        <v>485495</v>
       </c>
       <c r="R16" t="n">
-        <v>6850468</v>
+        <v>6850520</v>
       </c>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2241,7 +2259,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124718385</v>
+        <v>124717758</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2274,29 +2292,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>485387</v>
+        <v>485495</v>
       </c>
       <c r="R17" t="n">
-        <v>6850441</v>
+        <v>6850459</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2352,7 +2361,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124717615</v>
+        <v>124718500</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2385,26 +2394,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>485502</v>
+        <v>485369</v>
       </c>
       <c r="R18" t="n">
-        <v>6850463</v>
+        <v>6850446</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 59348-2020 artfynd.xlsx
+++ b/artfynd/A 59348-2020 artfynd.xlsx
@@ -1425,7 +1425,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124718448</v>
+        <v>124719083</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1458,17 +1458,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485375</v>
+        <v>485248</v>
       </c>
       <c r="R9" t="n">
-        <v>6850440</v>
+        <v>6850480</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124719083</v>
+        <v>124718448</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1560,26 +1569,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485248</v>
+        <v>485375</v>
       </c>
       <c r="R10" t="n">
-        <v>6850480</v>
+        <v>6850440</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 59348-2020 artfynd.xlsx
+++ b/artfynd/A 59348-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124717615</v>
+        <v>124718616</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -708,23 +708,14 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>485502</v>
+        <v>485358</v>
       </c>
       <c r="R2" t="n">
         <v>6850463</v>
@@ -786,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124716407</v>
+        <v>124718448</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -826,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>485304</v>
+        <v>485375</v>
       </c>
       <c r="R3" t="n">
-        <v>6850518</v>
+        <v>6850440</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124718815</v>
+        <v>124718500</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -928,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>485309</v>
+        <v>485369</v>
       </c>
       <c r="R4" t="n">
-        <v>6850480</v>
+        <v>6850446</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124718018</v>
+        <v>124719083</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1025,7 +1016,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1039,13 +1030,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485514</v>
+        <v>485248</v>
       </c>
       <c r="R5" t="n">
-        <v>6850415</v>
+        <v>6850480</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,7 +1092,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124718947</v>
+        <v>124717615</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1150,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485309</v>
+        <v>485502</v>
       </c>
       <c r="R6" t="n">
-        <v>6850483</v>
+        <v>6850463</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1203,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124718616</v>
+        <v>124718696</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1252,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>485358</v>
+        <v>485342</v>
       </c>
       <c r="R7" t="n">
-        <v>6850463</v>
+        <v>6850467</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1305,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124717816</v>
+        <v>124717758</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1347,29 +1338,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485493</v>
+        <v>485495</v>
       </c>
       <c r="R8" t="n">
-        <v>6850463</v>
+        <v>6850459</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1425,7 +1407,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124719083</v>
+        <v>124717289</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1458,29 +1440,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485248</v>
+        <v>485495</v>
       </c>
       <c r="R9" t="n">
-        <v>6850480</v>
+        <v>6850520</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1536,7 +1509,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124718448</v>
+        <v>124718385</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1569,17 +1542,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485375</v>
+        <v>485387</v>
       </c>
       <c r="R10" t="n">
-        <v>6850440</v>
+        <v>6850441</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,7 +1620,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124717925</v>
+        <v>124717816</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1671,7 +1653,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
@@ -1681,10 +1672,10 @@
         <v>485493</v>
       </c>
       <c r="R11" t="n">
-        <v>6850455</v>
+        <v>6850463</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1842,7 +1833,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124717545</v>
+        <v>124718018</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1875,20 +1866,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485515</v>
+        <v>485514</v>
       </c>
       <c r="R13" t="n">
-        <v>6850468</v>
+        <v>6850415</v>
       </c>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124718696</v>
+        <v>124717545</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -1984,13 +1984,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485342</v>
+        <v>485515</v>
       </c>
       <c r="R14" t="n">
-        <v>6850467</v>
+        <v>6850468</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124718385</v>
+        <v>124718947</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2095,10 +2095,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485387</v>
+        <v>485309</v>
       </c>
       <c r="R15" t="n">
-        <v>6850441</v>
+        <v>6850483</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2157,7 +2157,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124717289</v>
+        <v>124716407</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2197,13 +2197,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>485495</v>
+        <v>485304</v>
       </c>
       <c r="R16" t="n">
-        <v>6850520</v>
+        <v>6850518</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124717758</v>
+        <v>124717925</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>485495</v>
+        <v>485493</v>
       </c>
       <c r="R17" t="n">
-        <v>6850459</v>
+        <v>6850455</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2361,7 +2361,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124718500</v>
+        <v>124718815</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2401,10 +2401,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>485369</v>
+        <v>485309</v>
       </c>
       <c r="R18" t="n">
-        <v>6850446</v>
+        <v>6850480</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 59348-2020 artfynd.xlsx
+++ b/artfynd/A 59348-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124718616</v>
+        <v>124718696</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>485358</v>
+        <v>485342</v>
       </c>
       <c r="R2" t="n">
-        <v>6850463</v>
+        <v>6850467</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124718448</v>
+        <v>124717545</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>485375</v>
+        <v>485515</v>
       </c>
       <c r="R3" t="n">
-        <v>6850440</v>
+        <v>6850468</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124718500</v>
+        <v>124716407</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>485369</v>
+        <v>485304</v>
       </c>
       <c r="R4" t="n">
-        <v>6850446</v>
+        <v>6850518</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124719083</v>
+        <v>124718448</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1014,26 +1014,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485248</v>
+        <v>485375</v>
       </c>
       <c r="R5" t="n">
-        <v>6850480</v>
+        <v>6850440</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124717615</v>
+        <v>124718815</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1125,26 +1116,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485502</v>
+        <v>485309</v>
       </c>
       <c r="R6" t="n">
-        <v>6850463</v>
+        <v>6850480</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124718696</v>
+        <v>124717615</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1236,17 +1218,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>485342</v>
+        <v>485502</v>
       </c>
       <c r="R7" t="n">
-        <v>6850467</v>
+        <v>6850463</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1296,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124717758</v>
+        <v>124718018</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1338,17 +1329,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485495</v>
+        <v>485514</v>
       </c>
       <c r="R8" t="n">
-        <v>6850459</v>
+        <v>6850415</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1407,7 +1407,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124717289</v>
+        <v>124717816</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1440,20 +1440,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485495</v>
+        <v>485493</v>
       </c>
       <c r="R9" t="n">
-        <v>6850520</v>
+        <v>6850463</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1509,7 +1518,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124718385</v>
+        <v>124718947</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1558,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485387</v>
+        <v>485309</v>
       </c>
       <c r="R10" t="n">
-        <v>6850441</v>
+        <v>6850483</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1620,7 +1629,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124717816</v>
+        <v>124718500</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1653,26 +1662,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>485493</v>
+        <v>485369</v>
       </c>
       <c r="R11" t="n">
-        <v>6850463</v>
+        <v>6850446</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1731,7 +1731,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124719045</v>
+        <v>124718616</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1771,10 +1771,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485262</v>
+        <v>485358</v>
       </c>
       <c r="R12" t="n">
-        <v>6850477</v>
+        <v>6850463</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1833,7 +1833,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124718018</v>
+        <v>124717758</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1866,26 +1866,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485514</v>
+        <v>485495</v>
       </c>
       <c r="R13" t="n">
-        <v>6850415</v>
+        <v>6850459</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1944,7 +1935,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124717545</v>
+        <v>124719045</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -1984,13 +1975,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485515</v>
+        <v>485262</v>
       </c>
       <c r="R14" t="n">
-        <v>6850468</v>
+        <v>6850477</v>
       </c>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2046,7 +2037,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124718947</v>
+        <v>124718385</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2095,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485309</v>
+        <v>485387</v>
       </c>
       <c r="R15" t="n">
-        <v>6850483</v>
+        <v>6850441</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2157,7 +2148,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124716407</v>
+        <v>124719083</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2190,17 +2181,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>485304</v>
+        <v>485248</v>
       </c>
       <c r="R16" t="n">
-        <v>6850518</v>
+        <v>6850480</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2361,7 +2361,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124718815</v>
+        <v>124717289</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2401,13 +2401,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>485309</v>
+        <v>485495</v>
       </c>
       <c r="R18" t="n">
-        <v>6850480</v>
+        <v>6850520</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>

--- a/artfynd/A 59348-2020 artfynd.xlsx
+++ b/artfynd/A 59348-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124718696</v>
+        <v>124718947</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -708,17 +708,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>485342</v>
+        <v>485309</v>
       </c>
       <c r="R2" t="n">
-        <v>6850467</v>
+        <v>6850483</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124717545</v>
+        <v>124718616</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -817,13 +826,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>485515</v>
+        <v>485358</v>
       </c>
       <c r="R3" t="n">
-        <v>6850468</v>
+        <v>6850463</v>
       </c>
       <c r="S3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124716407</v>
+        <v>124717925</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -919,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>485304</v>
+        <v>485493</v>
       </c>
       <c r="R4" t="n">
-        <v>6850518</v>
+        <v>6850455</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124718448</v>
+        <v>124718018</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1014,20 +1023,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485375</v>
+        <v>485514</v>
       </c>
       <c r="R5" t="n">
-        <v>6850440</v>
+        <v>6850415</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1185,7 +1203,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124717615</v>
+        <v>124718448</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1218,26 +1236,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>485502</v>
+        <v>485375</v>
       </c>
       <c r="R7" t="n">
-        <v>6850463</v>
+        <v>6850440</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,7 +1305,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124718018</v>
+        <v>124719083</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1331,7 +1340,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1345,13 +1354,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485514</v>
+        <v>485248</v>
       </c>
       <c r="R8" t="n">
-        <v>6850415</v>
+        <v>6850480</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,7 +1416,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124717816</v>
+        <v>124716407</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1440,26 +1449,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485493</v>
+        <v>485304</v>
       </c>
       <c r="R9" t="n">
-        <v>6850463</v>
+        <v>6850518</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1518,7 +1518,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124718947</v>
+        <v>124719045</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1551,26 +1551,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485309</v>
+        <v>485262</v>
       </c>
       <c r="R10" t="n">
-        <v>6850483</v>
+        <v>6850477</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1731,7 +1722,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124718616</v>
+        <v>124718385</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1764,17 +1755,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485358</v>
+        <v>485387</v>
       </c>
       <c r="R12" t="n">
-        <v>6850463</v>
+        <v>6850441</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1935,7 +1935,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124719045</v>
+        <v>124717545</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -1975,13 +1975,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485262</v>
+        <v>485515</v>
       </c>
       <c r="R14" t="n">
-        <v>6850477</v>
+        <v>6850468</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124718385</v>
+        <v>124718696</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2070,26 +2070,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485387</v>
+        <v>485342</v>
       </c>
       <c r="R15" t="n">
-        <v>6850441</v>
+        <v>6850467</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,7 +2139,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124719083</v>
+        <v>124717289</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2181,29 +2172,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>485248</v>
+        <v>485495</v>
       </c>
       <c r="R16" t="n">
-        <v>6850480</v>
+        <v>6850520</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2259,7 +2241,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124717925</v>
+        <v>124717615</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2292,20 +2274,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>485493</v>
+        <v>485502</v>
       </c>
       <c r="R17" t="n">
-        <v>6850455</v>
+        <v>6850463</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2361,7 +2352,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124717289</v>
+        <v>124717816</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2394,20 +2385,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>485495</v>
+        <v>485493</v>
       </c>
       <c r="R18" t="n">
-        <v>6850520</v>
+        <v>6850463</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>

--- a/artfynd/A 59348-2020 artfynd.xlsx
+++ b/artfynd/A 59348-2020 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124718616</v>
+        <v>124717289</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -826,13 +826,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>485358</v>
+        <v>485495</v>
       </c>
       <c r="R3" t="n">
-        <v>6850463</v>
+        <v>6850520</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124717925</v>
+        <v>124718500</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -928,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>485493</v>
+        <v>485369</v>
       </c>
       <c r="R4" t="n">
-        <v>6850455</v>
+        <v>6850446</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124718018</v>
+        <v>124718385</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1039,13 +1039,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485514</v>
+        <v>485387</v>
       </c>
       <c r="R5" t="n">
-        <v>6850415</v>
+        <v>6850441</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124718815</v>
+        <v>124719083</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1134,14 +1134,23 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485309</v>
+        <v>485248</v>
       </c>
       <c r="R6" t="n">
         <v>6850480</v>
@@ -1203,7 +1212,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124718448</v>
+        <v>124717816</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1236,17 +1245,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>485375</v>
+        <v>485493</v>
       </c>
       <c r="R7" t="n">
-        <v>6850440</v>
+        <v>6850463</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1323,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124719083</v>
+        <v>124718018</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1340,7 +1358,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1354,13 +1372,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485248</v>
+        <v>485514</v>
       </c>
       <c r="R8" t="n">
-        <v>6850480</v>
+        <v>6850415</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1416,7 +1434,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124716407</v>
+        <v>124717615</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1449,17 +1467,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485304</v>
+        <v>485502</v>
       </c>
       <c r="R9" t="n">
-        <v>6850518</v>
+        <v>6850463</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1518,7 +1545,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124719045</v>
+        <v>124718696</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1558,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485262</v>
+        <v>485342</v>
       </c>
       <c r="R10" t="n">
-        <v>6850477</v>
+        <v>6850467</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1620,7 +1647,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124718500</v>
+        <v>124717758</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1660,13 +1687,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>485369</v>
+        <v>485495</v>
       </c>
       <c r="R11" t="n">
-        <v>6850446</v>
+        <v>6850459</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1722,7 +1749,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124718385</v>
+        <v>124718616</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1755,26 +1782,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485387</v>
+        <v>485358</v>
       </c>
       <c r="R12" t="n">
-        <v>6850441</v>
+        <v>6850463</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1833,7 +1851,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124717758</v>
+        <v>124717925</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1873,10 +1891,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485495</v>
+        <v>485493</v>
       </c>
       <c r="R13" t="n">
-        <v>6850459</v>
+        <v>6850455</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2037,7 +2055,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124718696</v>
+        <v>124719045</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2077,10 +2095,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485342</v>
+        <v>485262</v>
       </c>
       <c r="R15" t="n">
-        <v>6850467</v>
+        <v>6850477</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2139,7 +2157,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124717289</v>
+        <v>124716407</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2179,13 +2197,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>485495</v>
+        <v>485304</v>
       </c>
       <c r="R16" t="n">
-        <v>6850520</v>
+        <v>6850518</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2241,7 +2259,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124717615</v>
+        <v>124718815</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2274,26 +2292,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>485502</v>
+        <v>485309</v>
       </c>
       <c r="R17" t="n">
-        <v>6850463</v>
+        <v>6850480</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2352,7 +2361,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124717816</v>
+        <v>124718448</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2385,26 +2394,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>485493</v>
+        <v>485375</v>
       </c>
       <c r="R18" t="n">
-        <v>6850463</v>
+        <v>6850440</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 59348-2020 artfynd.xlsx
+++ b/artfynd/A 59348-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124718947</v>
+        <v>124717289</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -708,29 +708,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>485309</v>
+        <v>485495</v>
       </c>
       <c r="R2" t="n">
-        <v>6850483</v>
+        <v>6850520</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124717289</v>
+        <v>124717615</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -819,20 +810,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>485495</v>
+        <v>485502</v>
       </c>
       <c r="R3" t="n">
-        <v>6850520</v>
+        <v>6850463</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124718500</v>
+        <v>124719045</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>485369</v>
+        <v>485262</v>
       </c>
       <c r="R4" t="n">
-        <v>6850446</v>
+        <v>6850477</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124718385</v>
+        <v>124718500</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1023,26 +1023,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485387</v>
+        <v>485369</v>
       </c>
       <c r="R5" t="n">
-        <v>6850441</v>
+        <v>6850446</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1092,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124719083</v>
+        <v>124718018</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1136,7 +1127,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1150,13 +1141,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485248</v>
+        <v>485514</v>
       </c>
       <c r="R6" t="n">
-        <v>6850480</v>
+        <v>6850415</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,7 +1203,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124717816</v>
+        <v>124718616</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1245,23 +1236,14 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>485493</v>
+        <v>485358</v>
       </c>
       <c r="R7" t="n">
         <v>6850463</v>
@@ -1323,7 +1305,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124718018</v>
+        <v>124717925</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1356,26 +1338,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485514</v>
+        <v>485493</v>
       </c>
       <c r="R8" t="n">
-        <v>6850415</v>
+        <v>6850455</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1434,7 +1407,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124717615</v>
+        <v>124717758</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1467,29 +1440,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485502</v>
+        <v>485495</v>
       </c>
       <c r="R9" t="n">
-        <v>6850463</v>
+        <v>6850459</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1647,7 +1611,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124717758</v>
+        <v>124718947</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1680,20 +1644,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>485495</v>
+        <v>485309</v>
       </c>
       <c r="R11" t="n">
-        <v>6850459</v>
+        <v>6850483</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1749,7 +1722,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124718616</v>
+        <v>124718815</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1789,10 +1762,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485358</v>
+        <v>485309</v>
       </c>
       <c r="R12" t="n">
-        <v>6850463</v>
+        <v>6850480</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1851,7 +1824,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124717925</v>
+        <v>124718448</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1891,13 +1864,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485493</v>
+        <v>485375</v>
       </c>
       <c r="R13" t="n">
-        <v>6850455</v>
+        <v>6850440</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2055,7 +2028,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124719045</v>
+        <v>124719083</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2088,17 +2061,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485262</v>
+        <v>485248</v>
       </c>
       <c r="R15" t="n">
-        <v>6850477</v>
+        <v>6850480</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2157,7 +2139,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124716407</v>
+        <v>124717816</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2190,17 +2172,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>485304</v>
+        <v>485493</v>
       </c>
       <c r="R16" t="n">
-        <v>6850518</v>
+        <v>6850463</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2259,7 +2250,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124718815</v>
+        <v>124718385</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2292,17 +2283,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>485309</v>
+        <v>485387</v>
       </c>
       <c r="R17" t="n">
-        <v>6850480</v>
+        <v>6850441</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2361,7 +2361,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124718448</v>
+        <v>124716407</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2401,10 +2401,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>485375</v>
+        <v>485304</v>
       </c>
       <c r="R18" t="n">
-        <v>6850440</v>
+        <v>6850518</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 59348-2020 artfynd.xlsx
+++ b/artfynd/A 59348-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124717289</v>
+        <v>124718616</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>485495</v>
+        <v>485358</v>
       </c>
       <c r="R2" t="n">
-        <v>6850520</v>
+        <v>6850463</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124717615</v>
+        <v>124718696</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -810,26 +810,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>485502</v>
+        <v>485342</v>
       </c>
       <c r="R3" t="n">
-        <v>6850463</v>
+        <v>6850467</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124719045</v>
+        <v>124716407</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -928,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>485262</v>
+        <v>485304</v>
       </c>
       <c r="R4" t="n">
-        <v>6850477</v>
+        <v>6850518</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124718500</v>
+        <v>124717289</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1030,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485369</v>
+        <v>485495</v>
       </c>
       <c r="R5" t="n">
-        <v>6850446</v>
+        <v>6850520</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1203,7 +1194,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124718616</v>
+        <v>124718500</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1243,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>485358</v>
+        <v>485369</v>
       </c>
       <c r="R7" t="n">
-        <v>6850463</v>
+        <v>6850446</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1407,7 +1398,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124717758</v>
+        <v>124719045</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1447,13 +1438,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485495</v>
+        <v>485262</v>
       </c>
       <c r="R9" t="n">
-        <v>6850459</v>
+        <v>6850477</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1509,7 +1500,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124718696</v>
+        <v>124718385</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1542,17 +1533,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485342</v>
+        <v>485387</v>
       </c>
       <c r="R10" t="n">
-        <v>6850467</v>
+        <v>6850441</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124718815</v>
+        <v>124717545</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1762,13 +1762,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485309</v>
+        <v>485515</v>
       </c>
       <c r="R12" t="n">
-        <v>6850480</v>
+        <v>6850468</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124718448</v>
+        <v>124717758</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1864,13 +1864,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485375</v>
+        <v>485495</v>
       </c>
       <c r="R13" t="n">
-        <v>6850440</v>
+        <v>6850459</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124717545</v>
+        <v>124718448</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -1966,13 +1966,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485515</v>
+        <v>485375</v>
       </c>
       <c r="R14" t="n">
-        <v>6850468</v>
+        <v>6850440</v>
       </c>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124718385</v>
+        <v>124717615</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>485387</v>
+        <v>485502</v>
       </c>
       <c r="R17" t="n">
-        <v>6850441</v>
+        <v>6850463</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2361,7 +2361,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124716407</v>
+        <v>124718815</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2401,10 +2401,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>485304</v>
+        <v>485309</v>
       </c>
       <c r="R18" t="n">
-        <v>6850518</v>
+        <v>6850480</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 59348-2020 artfynd.xlsx
+++ b/artfynd/A 59348-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124718616</v>
+        <v>124716407</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>485358</v>
+        <v>485304</v>
       </c>
       <c r="R2" t="n">
-        <v>6850463</v>
+        <v>6850518</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124718696</v>
+        <v>124718018</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -810,20 +810,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>485342</v>
+        <v>485514</v>
       </c>
       <c r="R3" t="n">
-        <v>6850467</v>
+        <v>6850415</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124716407</v>
+        <v>124717289</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -919,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>485304</v>
+        <v>485495</v>
       </c>
       <c r="R4" t="n">
-        <v>6850518</v>
+        <v>6850520</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124717289</v>
+        <v>124718500</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1021,13 +1030,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485495</v>
+        <v>485369</v>
       </c>
       <c r="R5" t="n">
-        <v>6850520</v>
+        <v>6850446</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,7 +1092,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124718018</v>
+        <v>124717545</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1116,29 +1125,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485514</v>
+        <v>485515</v>
       </c>
       <c r="R6" t="n">
-        <v>6850415</v>
+        <v>6850468</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124718500</v>
+        <v>124718385</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1227,17 +1227,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>485369</v>
+        <v>485387</v>
       </c>
       <c r="R7" t="n">
-        <v>6850446</v>
+        <v>6850441</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,7 +1305,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124717925</v>
+        <v>124718815</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1336,13 +1345,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485493</v>
+        <v>485309</v>
       </c>
       <c r="R8" t="n">
-        <v>6850455</v>
+        <v>6850480</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1398,7 +1407,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124719045</v>
+        <v>124718696</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1438,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485262</v>
+        <v>485342</v>
       </c>
       <c r="R9" t="n">
-        <v>6850477</v>
+        <v>6850467</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,7 +1509,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124718385</v>
+        <v>124719045</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1533,26 +1542,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485387</v>
+        <v>485262</v>
       </c>
       <c r="R10" t="n">
-        <v>6850441</v>
+        <v>6850477</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124718947</v>
+        <v>124717816</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1660,10 +1660,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>485309</v>
+        <v>485493</v>
       </c>
       <c r="R11" t="n">
-        <v>6850483</v>
+        <v>6850463</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124717545</v>
+        <v>124718448</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1762,13 +1762,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485515</v>
+        <v>485375</v>
       </c>
       <c r="R12" t="n">
-        <v>6850468</v>
+        <v>6850440</v>
       </c>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124717758</v>
+        <v>124718947</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1857,20 +1857,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485495</v>
+        <v>485309</v>
       </c>
       <c r="R13" t="n">
-        <v>6850459</v>
+        <v>6850483</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1926,7 +1935,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124718448</v>
+        <v>124719083</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -1959,17 +1968,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485375</v>
+        <v>485248</v>
       </c>
       <c r="R14" t="n">
-        <v>6850440</v>
+        <v>6850480</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2028,7 +2046,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124719083</v>
+        <v>124717758</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2061,29 +2079,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485248</v>
+        <v>485495</v>
       </c>
       <c r="R15" t="n">
-        <v>6850480</v>
+        <v>6850459</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2139,7 +2148,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124717816</v>
+        <v>124717925</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2172,16 +2181,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
@@ -2191,10 +2191,10 @@
         <v>485493</v>
       </c>
       <c r="R16" t="n">
-        <v>6850463</v>
+        <v>6850455</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124718815</v>
+        <v>124718616</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2401,10 +2401,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>485309</v>
+        <v>485358</v>
       </c>
       <c r="R18" t="n">
-        <v>6850480</v>
+        <v>6850463</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 59348-2020 artfynd.xlsx
+++ b/artfynd/A 59348-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124716407</v>
+        <v>124719083</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -708,17 +708,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>485304</v>
+        <v>485248</v>
       </c>
       <c r="R2" t="n">
-        <v>6850518</v>
+        <v>6850480</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124718018</v>
+        <v>124719045</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -810,29 +819,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>485514</v>
+        <v>485262</v>
       </c>
       <c r="R3" t="n">
-        <v>6850415</v>
+        <v>6850477</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124717289</v>
+        <v>124718815</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -928,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>485495</v>
+        <v>485309</v>
       </c>
       <c r="R4" t="n">
-        <v>6850520</v>
+        <v>6850480</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124718500</v>
+        <v>124716407</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485369</v>
+        <v>485304</v>
       </c>
       <c r="R5" t="n">
-        <v>6850446</v>
+        <v>6850518</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124717545</v>
+        <v>124717615</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1125,20 +1125,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485515</v>
+        <v>485502</v>
       </c>
       <c r="R6" t="n">
-        <v>6850468</v>
+        <v>6850463</v>
       </c>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1194,7 +1203,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124718385</v>
+        <v>124717758</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1227,29 +1236,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>485387</v>
+        <v>485495</v>
       </c>
       <c r="R7" t="n">
-        <v>6850441</v>
+        <v>6850459</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124718815</v>
+        <v>124717289</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1345,13 +1345,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485309</v>
+        <v>485495</v>
       </c>
       <c r="R8" t="n">
-        <v>6850480</v>
+        <v>6850520</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124718696</v>
+        <v>124718018</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1440,20 +1440,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485342</v>
+        <v>485514</v>
       </c>
       <c r="R9" t="n">
-        <v>6850467</v>
+        <v>6850415</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1509,7 +1518,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124719045</v>
+        <v>124718947</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1542,17 +1551,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485262</v>
+        <v>485309</v>
       </c>
       <c r="R10" t="n">
-        <v>6850477</v>
+        <v>6850483</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1629,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124717816</v>
+        <v>124717925</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1644,16 +1662,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
@@ -1663,10 +1672,10 @@
         <v>485493</v>
       </c>
       <c r="R11" t="n">
-        <v>6850463</v>
+        <v>6850455</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1824,7 +1833,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124718947</v>
+        <v>124718385</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1873,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485309</v>
+        <v>485387</v>
       </c>
       <c r="R13" t="n">
-        <v>6850483</v>
+        <v>6850441</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1935,7 +1944,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124719083</v>
+        <v>124718500</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -1968,26 +1977,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485248</v>
+        <v>485369</v>
       </c>
       <c r="R14" t="n">
-        <v>6850480</v>
+        <v>6850446</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2046,7 +2046,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124717758</v>
+        <v>124718616</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2086,13 +2086,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485495</v>
+        <v>485358</v>
       </c>
       <c r="R15" t="n">
-        <v>6850459</v>
+        <v>6850463</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124717925</v>
+        <v>124717816</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2181,7 +2181,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
@@ -2191,10 +2200,10 @@
         <v>485493</v>
       </c>
       <c r="R16" t="n">
-        <v>6850455</v>
+        <v>6850463</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2250,7 +2259,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124717615</v>
+        <v>124718696</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2283,26 +2292,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>485502</v>
+        <v>485342</v>
       </c>
       <c r="R17" t="n">
-        <v>6850463</v>
+        <v>6850467</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2361,7 +2361,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124718616</v>
+        <v>124717545</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2401,13 +2401,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>485358</v>
+        <v>485515</v>
       </c>
       <c r="R18" t="n">
-        <v>6850463</v>
+        <v>6850468</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>

--- a/artfynd/A 59348-2020 artfynd.xlsx
+++ b/artfynd/A 59348-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124719083</v>
+        <v>124717925</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -708,29 +708,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>485248</v>
+        <v>485493</v>
       </c>
       <c r="R2" t="n">
-        <v>6850480</v>
+        <v>6850455</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124719045</v>
+        <v>124718696</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -826,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>485262</v>
+        <v>485342</v>
       </c>
       <c r="R3" t="n">
-        <v>6850477</v>
+        <v>6850467</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124718815</v>
+        <v>124717816</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -921,17 +912,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>485309</v>
+        <v>485493</v>
       </c>
       <c r="R4" t="n">
-        <v>6850480</v>
+        <v>6850463</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124716407</v>
+        <v>124718947</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1023,17 +1023,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485304</v>
+        <v>485309</v>
       </c>
       <c r="R5" t="n">
-        <v>6850518</v>
+        <v>6850483</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,7 +1101,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124717615</v>
+        <v>124716407</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1125,26 +1134,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485502</v>
+        <v>485304</v>
       </c>
       <c r="R6" t="n">
-        <v>6850463</v>
+        <v>6850518</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1203,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124717758</v>
+        <v>124718018</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1236,17 +1236,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>485495</v>
+        <v>485514</v>
       </c>
       <c r="R7" t="n">
-        <v>6850459</v>
+        <v>6850415</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1305,7 +1314,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124717289</v>
+        <v>124717615</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1338,20 +1347,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485495</v>
+        <v>485502</v>
       </c>
       <c r="R8" t="n">
-        <v>6850520</v>
+        <v>6850463</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,7 +1425,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124718018</v>
+        <v>124718500</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1440,29 +1458,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485514</v>
+        <v>485369</v>
       </c>
       <c r="R9" t="n">
-        <v>6850415</v>
+        <v>6850446</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1518,7 +1527,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124718947</v>
+        <v>124718448</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1551,26 +1560,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485309</v>
+        <v>485375</v>
       </c>
       <c r="R10" t="n">
-        <v>6850483</v>
+        <v>6850440</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,7 +1629,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124717925</v>
+        <v>124719083</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1662,20 +1662,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>485493</v>
+        <v>485248</v>
       </c>
       <c r="R11" t="n">
-        <v>6850455</v>
+        <v>6850480</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1731,7 +1740,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124718448</v>
+        <v>124717289</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1771,13 +1780,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485375</v>
+        <v>485495</v>
       </c>
       <c r="R12" t="n">
-        <v>6850440</v>
+        <v>6850520</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1833,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124718385</v>
+        <v>124719045</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1866,26 +1875,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485387</v>
+        <v>485262</v>
       </c>
       <c r="R13" t="n">
-        <v>6850441</v>
+        <v>6850477</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1944,7 +1944,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124718500</v>
+        <v>124717545</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -1984,13 +1984,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485369</v>
+        <v>485515</v>
       </c>
       <c r="R14" t="n">
-        <v>6850446</v>
+        <v>6850468</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124718616</v>
+        <v>124718815</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485358</v>
+        <v>485309</v>
       </c>
       <c r="R15" t="n">
-        <v>6850463</v>
+        <v>6850480</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,7 +2148,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124717816</v>
+        <v>124717758</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2181,29 +2181,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>485493</v>
+        <v>485495</v>
       </c>
       <c r="R16" t="n">
-        <v>6850463</v>
+        <v>6850459</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2259,7 +2250,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124718696</v>
+        <v>124718385</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2292,17 +2283,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>485342</v>
+        <v>485387</v>
       </c>
       <c r="R17" t="n">
-        <v>6850467</v>
+        <v>6850441</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2361,7 +2361,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124717545</v>
+        <v>124718616</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2401,13 +2401,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>485515</v>
+        <v>485358</v>
       </c>
       <c r="R18" t="n">
-        <v>6850468</v>
+        <v>6850463</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>

--- a/artfynd/A 59348-2020 artfynd.xlsx
+++ b/artfynd/A 59348-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124717925</v>
+        <v>124718947</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -708,20 +708,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>485493</v>
+        <v>485309</v>
       </c>
       <c r="R2" t="n">
-        <v>6850455</v>
+        <v>6850483</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124718696</v>
+        <v>124717925</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -817,13 +826,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>485342</v>
+        <v>485493</v>
       </c>
       <c r="R3" t="n">
-        <v>6850467</v>
+        <v>6850455</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124717816</v>
+        <v>124718696</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -912,26 +921,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>485493</v>
+        <v>485342</v>
       </c>
       <c r="R4" t="n">
-        <v>6850463</v>
+        <v>6850467</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124718947</v>
+        <v>124719045</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1023,26 +1023,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485309</v>
+        <v>485262</v>
       </c>
       <c r="R5" t="n">
-        <v>6850483</v>
+        <v>6850477</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1092,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124716407</v>
+        <v>124718018</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1134,20 +1125,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485304</v>
+        <v>485514</v>
       </c>
       <c r="R6" t="n">
-        <v>6850518</v>
+        <v>6850415</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124718018</v>
+        <v>124719083</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1252,13 +1252,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>485514</v>
+        <v>485248</v>
       </c>
       <c r="R7" t="n">
-        <v>6850415</v>
+        <v>6850480</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124717615</v>
+        <v>124718448</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1347,26 +1347,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485502</v>
+        <v>485375</v>
       </c>
       <c r="R8" t="n">
-        <v>6850463</v>
+        <v>6850440</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,7 +1416,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124718500</v>
+        <v>124717816</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1458,17 +1449,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485369</v>
+        <v>485493</v>
       </c>
       <c r="R9" t="n">
-        <v>6850446</v>
+        <v>6850463</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124718448</v>
+        <v>124718385</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1560,17 +1560,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485375</v>
+        <v>485387</v>
       </c>
       <c r="R10" t="n">
-        <v>6850440</v>
+        <v>6850441</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124719083</v>
+        <v>124717289</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1662,29 +1671,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>485248</v>
+        <v>485495</v>
       </c>
       <c r="R11" t="n">
-        <v>6850480</v>
+        <v>6850520</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124717289</v>
+        <v>124717545</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1780,13 +1780,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485495</v>
+        <v>485515</v>
       </c>
       <c r="R12" t="n">
-        <v>6850520</v>
+        <v>6850468</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124719045</v>
+        <v>124716407</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485262</v>
+        <v>485304</v>
       </c>
       <c r="R13" t="n">
-        <v>6850477</v>
+        <v>6850518</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1944,7 +1944,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124717545</v>
+        <v>124718616</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -1984,13 +1984,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485515</v>
+        <v>485358</v>
       </c>
       <c r="R14" t="n">
-        <v>6850468</v>
+        <v>6850463</v>
       </c>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124718815</v>
+        <v>124717758</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2086,13 +2086,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485309</v>
+        <v>485495</v>
       </c>
       <c r="R15" t="n">
-        <v>6850480</v>
+        <v>6850459</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124717758</v>
+        <v>124718815</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2188,13 +2188,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>485495</v>
+        <v>485309</v>
       </c>
       <c r="R16" t="n">
-        <v>6850459</v>
+        <v>6850480</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124718385</v>
+        <v>124717615</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>485387</v>
+        <v>485502</v>
       </c>
       <c r="R17" t="n">
-        <v>6850441</v>
+        <v>6850463</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2361,7 +2361,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124718616</v>
+        <v>124718500</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2401,10 +2401,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>485358</v>
+        <v>485369</v>
       </c>
       <c r="R18" t="n">
-        <v>6850463</v>
+        <v>6850446</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 59348-2020 artfynd.xlsx
+++ b/artfynd/A 59348-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124718947</v>
+        <v>124717925</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -708,29 +708,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>485309</v>
+        <v>485493</v>
       </c>
       <c r="R2" t="n">
-        <v>6850483</v>
+        <v>6850455</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124717925</v>
+        <v>124717289</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -826,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>485493</v>
+        <v>485495</v>
       </c>
       <c r="R3" t="n">
-        <v>6850455</v>
+        <v>6850520</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124718696</v>
+        <v>124717758</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -928,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>485342</v>
+        <v>485495</v>
       </c>
       <c r="R4" t="n">
-        <v>6850467</v>
+        <v>6850459</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124719045</v>
+        <v>124718018</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1023,20 +1014,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485262</v>
+        <v>485514</v>
       </c>
       <c r="R5" t="n">
-        <v>6850477</v>
+        <v>6850415</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124718018</v>
+        <v>124719045</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1125,29 +1125,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485514</v>
+        <v>485262</v>
       </c>
       <c r="R6" t="n">
-        <v>6850415</v>
+        <v>6850477</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1314,7 +1305,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124718448</v>
+        <v>124717545</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1354,13 +1345,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485375</v>
+        <v>485515</v>
       </c>
       <c r="R8" t="n">
-        <v>6850440</v>
+        <v>6850468</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1416,7 +1407,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124717816</v>
+        <v>124718696</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1449,26 +1440,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485493</v>
+        <v>485342</v>
       </c>
       <c r="R9" t="n">
-        <v>6850463</v>
+        <v>6850467</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,7 +1509,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124718385</v>
+        <v>124718815</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1560,26 +1542,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485387</v>
+        <v>485309</v>
       </c>
       <c r="R10" t="n">
-        <v>6850441</v>
+        <v>6850480</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,7 +1611,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124717289</v>
+        <v>124717615</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1671,20 +1644,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>485495</v>
+        <v>485502</v>
       </c>
       <c r="R11" t="n">
-        <v>6850520</v>
+        <v>6850463</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1740,7 +1722,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124717545</v>
+        <v>124718385</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1773,20 +1755,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485515</v>
+        <v>485387</v>
       </c>
       <c r="R12" t="n">
-        <v>6850468</v>
+        <v>6850441</v>
       </c>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1842,7 +1833,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124716407</v>
+        <v>124718947</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1875,17 +1866,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485304</v>
+        <v>485309</v>
       </c>
       <c r="R13" t="n">
-        <v>6850518</v>
+        <v>6850483</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2046,7 +2046,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124717758</v>
+        <v>124718500</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2086,13 +2086,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485495</v>
+        <v>485369</v>
       </c>
       <c r="R15" t="n">
-        <v>6850459</v>
+        <v>6850446</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124718815</v>
+        <v>124716407</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>485309</v>
+        <v>485304</v>
       </c>
       <c r="R16" t="n">
-        <v>6850480</v>
+        <v>6850518</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2250,7 +2250,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124717615</v>
+        <v>124718448</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2283,26 +2283,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>485502</v>
+        <v>485375</v>
       </c>
       <c r="R17" t="n">
-        <v>6850463</v>
+        <v>6850440</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2361,7 +2352,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124718500</v>
+        <v>124717816</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2394,17 +2385,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>485369</v>
+        <v>485493</v>
       </c>
       <c r="R18" t="n">
-        <v>6850446</v>
+        <v>6850463</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 59348-2020 artfynd.xlsx
+++ b/artfynd/A 59348-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124717925</v>
+        <v>124717758</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>485493</v>
+        <v>485495</v>
       </c>
       <c r="R2" t="n">
-        <v>6850455</v>
+        <v>6850459</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124717289</v>
+        <v>124718385</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,20 +810,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>485495</v>
+        <v>485387</v>
       </c>
       <c r="R3" t="n">
-        <v>6850520</v>
+        <v>6850441</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124717758</v>
+        <v>124719045</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>485495</v>
+        <v>485262</v>
       </c>
       <c r="R4" t="n">
-        <v>6850459</v>
+        <v>6850477</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124718018</v>
+        <v>124718947</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,7 +1025,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1030,13 +1039,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485514</v>
+        <v>485309</v>
       </c>
       <c r="R5" t="n">
-        <v>6850415</v>
+        <v>6850483</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124719045</v>
+        <v>124718448</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485262</v>
+        <v>485375</v>
       </c>
       <c r="R6" t="n">
-        <v>6850477</v>
+        <v>6850440</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124719083</v>
+        <v>124716407</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,26 +1236,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>485248</v>
+        <v>485304</v>
       </c>
       <c r="R7" t="n">
-        <v>6850480</v>
+        <v>6850518</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124717545</v>
+        <v>124718815</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,13 +1345,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485515</v>
+        <v>485309</v>
       </c>
       <c r="R8" t="n">
-        <v>6850468</v>
+        <v>6850480</v>
       </c>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124718696</v>
+        <v>124718500</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485342</v>
+        <v>485369</v>
       </c>
       <c r="R9" t="n">
-        <v>6850467</v>
+        <v>6850446</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,10 +1509,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124718815</v>
+        <v>124719083</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,14 +1542,23 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485309</v>
+        <v>485248</v>
       </c>
       <c r="R10" t="n">
         <v>6850480</v>
@@ -1614,7 +1623,7 @@
         <v>124717615</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,10 +1731,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124718385</v>
+        <v>124717816</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1771,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485387</v>
+        <v>485493</v>
       </c>
       <c r="R12" t="n">
-        <v>6850441</v>
+        <v>6850463</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1833,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124718947</v>
+        <v>124718616</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1866,26 +1875,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485309</v>
+        <v>485358</v>
       </c>
       <c r="R13" t="n">
-        <v>6850483</v>
+        <v>6850463</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1944,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124718616</v>
+        <v>124717545</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1984,13 +1984,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485358</v>
+        <v>485515</v>
       </c>
       <c r="R14" t="n">
-        <v>6850463</v>
+        <v>6850468</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124718500</v>
+        <v>124717925</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2086,13 +2086,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485369</v>
+        <v>485493</v>
       </c>
       <c r="R15" t="n">
-        <v>6850446</v>
+        <v>6850455</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2148,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124716407</v>
+        <v>124718018</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2181,20 +2181,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>485304</v>
+        <v>485514</v>
       </c>
       <c r="R16" t="n">
-        <v>6850518</v>
+        <v>6850415</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2250,10 +2259,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124718448</v>
+        <v>124718696</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2290,10 +2299,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>485375</v>
+        <v>485342</v>
       </c>
       <c r="R17" t="n">
-        <v>6850440</v>
+        <v>6850467</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2352,10 +2361,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124717816</v>
+        <v>124717289</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2385,29 +2394,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Näveråsen, Näveråsen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>485493</v>
+        <v>485495</v>
       </c>
       <c r="R18" t="n">
-        <v>6850463</v>
+        <v>6850520</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>

--- a/artfynd/A 59348-2020 artfynd.xlsx
+++ b/artfynd/A 59348-2020 artfynd.xlsx
@@ -1620,7 +1620,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124717615</v>
+        <v>124717816</v>
       </c>
       <c r="B11" t="n">
         <v>98269</v>
@@ -1669,7 +1669,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>485502</v>
+        <v>485493</v>
       </c>
       <c r="R11" t="n">
         <v>6850463</v>
@@ -1731,7 +1731,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124717816</v>
+        <v>124717615</v>
       </c>
       <c r="B12" t="n">
         <v>98269</v>
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485493</v>
+        <v>485502</v>
       </c>
       <c r="R12" t="n">
         <v>6850463</v>
